--- a/outputs/9111.xlsx
+++ b/outputs/9111.xlsx
@@ -246,36 +246,40 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true" readingOrder="1"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -283,23 +287,23 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -315,15 +319,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -592,334 +596,334 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="2" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="5" style="1" width="8.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="14.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="3" width="14.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="3" width="12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="20.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D1" s="3" t="str">
+      <c r="D1" s="4" t="str">
         <f aca="false" t="array" ref="D1:D1">IF((C1="")*(B1=""),"",_xlfn.IFNA(IF(C1=$J$2:$J$6,VLOOKUP($C1,$J$2:$K$6,2,FALSE()),IF(_xlfn.IFNA(VLOOKUP(B1,$G$2:$H$13,2,FALSE()),),VLOOKUP(B1,$G$2:$H$13,2,0),IF(C1=$J$2:$K$6,INDEX($J$2:$K$6,MATCH(C1,$J$2:$J$6,0),2),VLOOKUP($C1,$J$2:$K$6,2,FALSE())))),"2500"))</f>
         <v/>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="5" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="20.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="8" t="n">
-        <f aca="false">IF(AND(B2="",C2=""),"",IF(COUNTIF($G$2:$G$13,B2)&gt;0,VLOOKUP(B2,$G$2:$H$13,2,FALSE()),IF(COUNTIF($J$2:$J$6,C2)&gt;0,VLOOKUP(C2,$J$2:$K$6,2,FALSE()),2500)))</f>
+      <c r="D2" s="9" t="n">
+        <f aca="false">IF(AND(B2="",C2=""),"",IFERROR(VLOOKUP(B2,$G$2:$H$13,2,FALSE()),IFERROR(VLOOKUP(C2,$J$2:$K$6,2,FALSE()),2500)))</f>
         <v>6678</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="10" t="n">
+      <c r="H2" s="11" t="n">
         <v>1320</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="J2" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="K2" s="12" t="n">
+      <c r="K2" s="13" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="20.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="14" t="n">
-        <f aca="false">IF(AND(B3="",C3=""),"",IF(COUNTIF($G$2:$G$13,B3)&gt;0,VLOOKUP(B3,$G$2:$H$13,2,FALSE()),IF(COUNTIF($J$2:$J$6,C3)&gt;0,VLOOKUP(C3,$J$2:$K$6,2,FALSE()),2500)))</f>
+      <c r="D3" s="15" t="n">
+        <f aca="false">IF(AND(B3="",C3=""),"",IFERROR(VLOOKUP(B3,$G$2:$H$13,2,FALSE()),IFERROR(VLOOKUP(C3,$J$2:$K$6,2,FALSE()),2500)))</f>
         <v>3628</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="10" t="n">
+      <c r="H3" s="11" t="n">
         <v>2563</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="12" t="n">
+      <c r="K3" s="13" t="n">
         <v>3628</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="20.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="14" t="str">
-        <f aca="false">IF(AND(B4="",C4=""),"",IF(COUNTIF($G$2:$G$13,B4)&gt;0,VLOOKUP(B4,$G$2:$H$13,2,FALSE()),IF(COUNTIF($J$2:$J$6,C4)&gt;0,VLOOKUP(C4,$J$2:$K$6,2,FALSE()),2500)))</f>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="15" t="str">
+        <f aca="false">IF(AND(B4="",C4=""),"",IFERROR(VLOOKUP(B4,$G$2:$H$13,2,FALSE()),IFERROR(VLOOKUP(C4,$J$2:$K$6,2,FALSE()),2500)))</f>
         <v/>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="10" t="n">
+      <c r="H4" s="11" t="n">
         <v>2314</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="K4" s="12" t="n">
+      <c r="K4" s="13" t="n">
         <v>8920</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="20.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="7" t="s">
+      <c r="B5" s="14"/>
+      <c r="C5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="15" t="n">
-        <f aca="false">IF(AND(B5="",C5=""),"",IF(COUNTIF($G$2:$G$13,B5)&gt;0,VLOOKUP(B5,$G$2:$H$13,2,FALSE()),IF(COUNTIF($J$2:$J$6,C5)&gt;0,VLOOKUP(C5,$J$2:$K$6,2,FALSE()),2500)))</f>
+      <c r="D5" s="16" t="n">
+        <f aca="false">IF(AND(B5="",C5=""),"",IFERROR(VLOOKUP(B5,$G$2:$H$13,2,FALSE()),IFERROR(VLOOKUP(C5,$J$2:$K$6,2,FALSE()),2500)))</f>
         <v>3016</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="10" t="n">
+      <c r="H5" s="11" t="n">
         <v>98</v>
       </c>
-      <c r="J5" s="11" t="s">
+      <c r="J5" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="12" t="n">
+      <c r="K5" s="13" t="n">
         <v>201</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="20.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13" t="s">
+      <c r="B6" s="14"/>
+      <c r="C6" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="16" t="n">
-        <f aca="false">IF(AND(B6="",C6=""),"",IF(COUNTIF($G$2:$G$13,B6)&gt;0,VLOOKUP(B6,$G$2:$H$13,2,FALSE()),IF(COUNTIF($J$2:$J$6,C6)&gt;0,VLOOKUP(C6,$J$2:$K$6,2,FALSE()),2500)))</f>
+      <c r="D6" s="17" t="n">
+        <f aca="false">IF(AND(B6="",C6=""),"",IFERROR(VLOOKUP(B6,$G$2:$H$13,2,FALSE()),IFERROR(VLOOKUP(C6,$J$2:$K$6,2,FALSE()),2500)))</f>
         <v>2500</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="10" t="n">
+      <c r="H6" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="K6" s="12" t="n">
+      <c r="K6" s="13" t="n">
         <v>3016</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="20.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="15" t="n">
-        <f aca="false">IF(AND(B7="",C7=""),"",IF(COUNTIF($G$2:$G$13,B7)&gt;0,VLOOKUP(B7,$G$2:$H$13,2,FALSE()),IF(COUNTIF($J$2:$J$6,C7)&gt;0,VLOOKUP(C7,$J$2:$K$6,2,FALSE()),2500)))</f>
+      <c r="D7" s="16" t="n">
+        <f aca="false">IF(AND(B7="",C7=""),"",IFERROR(VLOOKUP(B7,$G$2:$H$13,2,FALSE()),IFERROR(VLOOKUP(C7,$J$2:$K$6,2,FALSE()),2500)))</f>
         <v>201</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="10" t="n">
+      <c r="H7" s="11" t="n">
         <v>1222</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="20.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
-      <c r="G8" s="9" t="s">
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="15"/>
+      <c r="G8" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="10" t="n">
+      <c r="H8" s="11" t="n">
         <v>2586</v>
       </c>
-      <c r="J8" s="17" t="s">
+      <c r="J8" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="K8" s="17"/>
+      <c r="K8" s="18"/>
     </row>
     <row r="9" customFormat="false" ht="20.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="14"/>
-      <c r="G9" s="9" t="s">
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="15"/>
+      <c r="G9" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="10" t="n">
+      <c r="H9" s="11" t="n">
         <v>3950</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="20.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="14"/>
-      <c r="G10" s="9" t="s">
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="15"/>
+      <c r="G10" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="H10" s="10" t="n">
+      <c r="H10" s="11" t="n">
         <v>5314</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="20.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="14"/>
-      <c r="G11" s="9" t="s">
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="15"/>
+      <c r="G11" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="H11" s="10" t="n">
+      <c r="H11" s="11" t="n">
         <v>6678</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="20.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14"/>
-      <c r="G12" s="9" t="s">
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="15"/>
+      <c r="G12" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="H12" s="10" t="n">
+      <c r="H12" s="11" t="n">
         <v>8042</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="20.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="14"/>
-      <c r="G13" s="9" t="s">
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="15"/>
+      <c r="G13" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="H13" s="10" t="n">
+      <c r="H13" s="11" t="n">
         <v>9406</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="20.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="5"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="20.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="5"/>
-      <c r="G15" s="17" t="s">
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="6"/>
+      <c r="G15" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="H15" s="17"/>
+      <c r="H15" s="18"/>
     </row>
     <row r="16" customFormat="false" ht="20.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="5"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="6"/>
     </row>
     <row r="17" customFormat="false" ht="20.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="5"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="6"/>
     </row>
     <row r="18" customFormat="false" ht="20.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="5"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="6"/>
     </row>
     <row r="19" customFormat="false" ht="20.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="5"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="6"/>
     </row>
     <row r="20" customFormat="false" ht="20.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="5"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="6"/>
     </row>
     <row r="21" customFormat="false" ht="20.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
+      <c r="A21" s="19"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
     </row>
     <row r="22" customFormat="false" ht="20.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="19"/>
+      <c r="B22" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/outputs/9111.xlsx
+++ b/outputs/9111.xlsx
@@ -629,8 +629,8 @@
         <v>5</v>
       </c>
       <c r="D2" s="9" t="n">
-        <f aca="false">IF(AND(B2="",C2=""),"",IFERROR(VLOOKUP(B2,$G$2:$H$13,2,FALSE()),IFERROR(VLOOKUP(C2,$J$2:$K$6,2,FALSE()),2500)))</f>
-        <v>6678</v>
+        <f aca="false" t="array" ref="D2:D2">IF(AND(B2="",C2=""),"",IF(ISNUMBER(MATCH(B2,$N$2:$N$13,0)),INDEX($O$2:$O$13,MATCH(B2,$N$2:$N$13,0)),IF(ISNUMBER(MATCH(C2,$J$2:$J$6,0)),INDEX($K$2:$K$6,MATCH(C2,$J$2:$J$6,0)),2500)))</f>
+        <v>3016</v>
       </c>
       <c r="G2" s="10" t="s">
         <v>6</v>
@@ -656,7 +656,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="15" t="n">
-        <f aca="false">IF(AND(B3="",C3=""),"",IFERROR(VLOOKUP(B3,$G$2:$H$13,2,FALSE()),IFERROR(VLOOKUP(C3,$J$2:$K$6,2,FALSE()),2500)))</f>
+        <f aca="false" t="array" ref="D3:D3">IF(AND(B3="",C3=""),"",IF(ISNUMBER(MATCH(B3,$N$2:$N$13,0)),INDEX($O$2:$O$13,MATCH(B3,$N$2:$N$13,0)),IF(ISNUMBER(MATCH(C3,$J$2:$J$6,0)),INDEX($K$2:$K$6,MATCH(C3,$J$2:$J$6,0)),2500)))</f>
         <v>3628</v>
       </c>
       <c r="G3" s="10" t="s">
@@ -679,7 +679,7 @@
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
       <c r="D4" s="15" t="str">
-        <f aca="false">IF(AND(B4="",C4=""),"",IFERROR(VLOOKUP(B4,$G$2:$H$13,2,FALSE()),IFERROR(VLOOKUP(C4,$J$2:$K$6,2,FALSE()),2500)))</f>
+        <f aca="false" t="array" ref="D4:D4">IF(AND(B4="",C4=""),"",IF(ISNUMBER(MATCH(B4,$N$2:$N$13,0)),INDEX($O$2:$O$13,MATCH(B4,$N$2:$N$13,0)),IF(ISNUMBER(MATCH(C4,$J$2:$J$6,0)),INDEX($K$2:$K$6,MATCH(C4,$J$2:$J$6,0)),2500)))</f>
         <v/>
       </c>
       <c r="G4" s="10" t="s">
@@ -704,7 +704,7 @@
         <v>5</v>
       </c>
       <c r="D5" s="16" t="n">
-        <f aca="false">IF(AND(B5="",C5=""),"",IFERROR(VLOOKUP(B5,$G$2:$H$13,2,FALSE()),IFERROR(VLOOKUP(C5,$J$2:$K$6,2,FALSE()),2500)))</f>
+        <f aca="false" t="array" ref="D5:D5">IF(AND(B5="",C5=""),"",IF(ISNUMBER(MATCH(B5,$N$2:$N$13,0)),INDEX($O$2:$O$13,MATCH(B5,$N$2:$N$13,0)),IF(ISNUMBER(MATCH(C5,$J$2:$J$6,0)),INDEX($K$2:$K$6,MATCH(C5,$J$2:$J$6,0)),2500)))</f>
         <v>3016</v>
       </c>
       <c r="G5" s="10" t="s">
@@ -729,7 +729,7 @@
         <v>15</v>
       </c>
       <c r="D6" s="17" t="n">
-        <f aca="false">IF(AND(B6="",C6=""),"",IFERROR(VLOOKUP(B6,$G$2:$H$13,2,FALSE()),IFERROR(VLOOKUP(C6,$J$2:$K$6,2,FALSE()),2500)))</f>
+        <f aca="false" t="array" ref="D6:D6">IF(AND(B6="",C6=""),"",IF(ISNUMBER(MATCH(B6,$N$2:$N$13,0)),INDEX($O$2:$O$13,MATCH(B6,$N$2:$N$13,0)),IF(ISNUMBER(MATCH(C6,$J$2:$J$6,0)),INDEX($K$2:$K$6,MATCH(C6,$J$2:$J$6,0)),2500)))</f>
         <v>2500</v>
       </c>
       <c r="G6" s="10" t="s">
@@ -756,7 +756,7 @@
         <v>14</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">IF(AND(B7="",C7=""),"",IFERROR(VLOOKUP(B7,$G$2:$H$13,2,FALSE()),IFERROR(VLOOKUP(C7,$J$2:$K$6,2,FALSE()),2500)))</f>
+        <f aca="false" t="array" ref="D7:D7">IF(AND(B7="",C7=""),"",IF(ISNUMBER(MATCH(B7,$N$2:$N$13,0)),INDEX($O$2:$O$13,MATCH(B7,$N$2:$N$13,0)),IF(ISNUMBER(MATCH(C7,$J$2:$J$6,0)),INDEX($K$2:$K$6,MATCH(C7,$J$2:$J$6,0)),2500)))</f>
         <v>201</v>
       </c>
       <c r="G7" s="10" t="s">
